--- a/DataFile/datafile.xlsx
+++ b/DataFile/datafile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x1016008\PycharmProjects\ShopB2Wise\DataFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B715F24D-0ED2-4888-A53D-74D8DE791335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D52815E1-85F8-441D-B71F-1AD801FAB7B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="10060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Addition" sheetId="1" r:id="rId1"/>
@@ -26,14 +26,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="40">
   <si>
     <t>TestCase</t>
   </si>
   <si>
-    <t>Rx-Capture: Select and dispense the switch item from the advertisement banner.</t>
-  </si>
-  <si>
     <t>SKU1</t>
   </si>
   <si>
@@ -88,12 +85,6 @@
     <t>Wireless Headphones</t>
   </si>
   <si>
-    <t>action1</t>
-  </si>
-  <si>
-    <t>decrease</t>
-  </si>
-  <si>
     <t>RemoveQty1</t>
   </si>
   <si>
@@ -116,6 +107,45 @@
   </si>
   <si>
     <t>RemoveQty8</t>
+  </si>
+  <si>
+    <t>Smart Watch</t>
+  </si>
+  <si>
+    <t>Add One Item to Cart</t>
+  </si>
+  <si>
+    <t>Add Multiple Items to Cart</t>
+  </si>
+  <si>
+    <t>Add all Items to Cart</t>
+  </si>
+  <si>
+    <t>Mechanical Keyboard</t>
+  </si>
+  <si>
+    <t>Desk Lamp</t>
+  </si>
+  <si>
+    <t>Coffee Maker</t>
+  </si>
+  <si>
+    <t>Running Shoes</t>
+  </si>
+  <si>
+    <t>Yoga Mat</t>
+  </si>
+  <si>
+    <t>Backpack</t>
+  </si>
+  <si>
+    <t>Partial Clear One Item from Cart</t>
+  </si>
+  <si>
+    <t>Remove One Item from Cart</t>
+  </si>
+  <si>
+    <t>Clear Cart</t>
   </si>
 </sst>
 </file>
@@ -446,62 +476,61 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="68.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="5" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>8</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
-      </c>
-      <c r="K1" t="s">
-        <v>6</v>
       </c>
       <c r="L1" t="s">
         <v>11</v>
@@ -521,64 +550,164 @@
       <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="H4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4">
+        <v>8</v>
+      </c>
+      <c r="J4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" t="s">
-        <v>18</v>
-      </c>
-      <c r="O2" t="s">
-        <v>18</v>
-      </c>
-      <c r="P2" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R2" t="s">
-        <v>18</v>
+      <c r="L4" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4">
+        <v>4</v>
+      </c>
+      <c r="N4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4">
+        <v>2</v>
+      </c>
+      <c r="P4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q4">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -590,7 +719,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B666F93E-0D52-4998-B04F-BF60BB25635F}">
-  <dimension ref="A1:Y2"/>
+  <dimension ref="A1:Y4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="68.90625" bestFit="1" customWidth="1"/>
@@ -625,152 +754,306 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" t="s">
         <v>22</v>
       </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="N1" t="s">
+        <v>5</v>
+      </c>
+      <c r="O1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="Q1" t="s">
+        <v>11</v>
+      </c>
+      <c r="R1" t="s">
+        <v>12</v>
+      </c>
+      <c r="S1" t="s">
         <v>24</v>
       </c>
-      <c r="K1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="T1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U1" t="s">
+        <v>14</v>
+      </c>
+      <c r="V1" t="s">
         <v>25</v>
       </c>
-      <c r="N1" t="s">
-        <v>6</v>
-      </c>
-      <c r="O1" t="s">
-        <v>11</v>
-      </c>
-      <c r="P1" t="s">
+      <c r="W1" t="s">
+        <v>15</v>
+      </c>
+      <c r="X1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y1" t="s">
         <v>26</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>12</v>
-      </c>
-      <c r="R1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S1" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" t="s">
-        <v>14</v>
-      </c>
-      <c r="U1" t="s">
-        <v>15</v>
-      </c>
-      <c r="V1" t="s">
-        <v>28</v>
-      </c>
-      <c r="W1" t="s">
-        <v>16</v>
-      </c>
-      <c r="X1" t="s">
-        <v>17</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2">
         <v>6</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>17</v>
+      </c>
+      <c r="R2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" t="s">
+        <v>17</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2" t="s">
+        <v>17</v>
+      </c>
+      <c r="X2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" t="s">
         <v>18</v>
       </c>
-      <c r="F2" t="s">
+      <c r="C3">
+        <v>6</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3" t="s">
+        <v>17</v>
+      </c>
+      <c r="U3" t="s">
+        <v>17</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3" t="s">
+        <v>17</v>
+      </c>
+      <c r="X3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s">
         <v>18</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>18</v>
-      </c>
-      <c r="O2" t="s">
-        <v>18</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R2" t="s">
-        <v>18</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2" t="s">
-        <v>18</v>
-      </c>
-      <c r="U2" t="s">
-        <v>18</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2" t="s">
-        <v>18</v>
-      </c>
-      <c r="X2" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y2">
+      <c r="C4">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4">
+        <v>6</v>
+      </c>
+      <c r="G4">
+        <v>6</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>17</v>
+      </c>
+      <c r="O4" t="s">
+        <v>17</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>17</v>
+      </c>
+      <c r="R4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4" t="s">
+        <v>17</v>
+      </c>
+      <c r="U4" t="s">
+        <v>17</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4" t="s">
+        <v>17</v>
+      </c>
+      <c r="X4" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y4">
         <v>0</v>
       </c>
     </row>

--- a/DataFile/datafile.xlsx
+++ b/DataFile/datafile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x1016008\PycharmProjects\ShopB2Wise\DataFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D52815E1-85F8-441D-B71F-1AD801FAB7B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D03519-6CAB-4A30-A657-11F08A027279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="10060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/DataFile/datafile.xlsx
+++ b/DataFile/datafile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x1016008\PycharmProjects\ShopB2Wise\DataFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D03519-6CAB-4A30-A657-11F08A027279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE2A2A9-408B-4570-AB0C-1A2DAD38B256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="10060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Addition" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="40">
   <si>
     <t>TestCase</t>
   </si>
@@ -477,12 +477,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
@@ -494,11 +494,11 @@
     <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -551,7 +551,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>28</v>
       </c>
@@ -604,7 +604,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>29</v>
       </c>
@@ -612,13 +612,13 @@
         <v>18</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
         <v>31</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3" t="s">
         <v>17</v>
@@ -654,10 +654,10 @@
         <v>32</v>
       </c>
       <c r="Q3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>30</v>
       </c>
@@ -665,7 +665,7 @@
         <v>18</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" t="s">
         <v>31</v>
@@ -677,37 +677,37 @@
         <v>33</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H4" t="s">
         <v>34</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J4" t="s">
         <v>35</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L4" t="s">
         <v>36</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N4" t="s">
         <v>27</v>
       </c>
       <c r="O4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P4" t="s">
         <v>32</v>
       </c>
       <c r="Q4">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -720,36 +720,36 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B666F93E-0D52-4998-B04F-BF60BB25635F}">
   <dimension ref="A1:Y4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="68.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="68.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="5" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="9" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="9" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="5" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="9" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -826,9 +826,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
@@ -840,10 +840,10 @@
         <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2">
-        <v>6</v>
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -903,9 +903,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
@@ -914,7 +914,7 @@
         <v>6</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E3" t="s">
         <v>27</v>
@@ -923,7 +923,7 @@
         <v>6</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
@@ -980,9 +980,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
@@ -991,7 +991,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E4" t="s">
         <v>27</v>
@@ -1000,7 +1000,7 @@
         <v>6</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
